--- a/BVSimulationFiles/83.xlsx
+++ b/BVSimulationFiles/83.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009643605870020965</v>
+        <v>0.001928721174004193</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/83.xlsx
+++ b/BVSimulationFiles/83.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001928721174004193</v>
+        <v>0.01928721174004193</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/83.xlsx
+++ b/BVSimulationFiles/83.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.002518421052631579</v>
+        <v>0.00165</v>
       </c>
       <c r="D1" t="n">
-        <v>0.005036842105263158</v>
+        <v>0.0033</v>
       </c>
       <c r="E1" t="n">
-        <v>0.007555263157894739</v>
+        <v>0.00495</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01007368421052632</v>
+        <v>0.0066</v>
       </c>
       <c r="G1" t="n">
-        <v>0.0125921052631579</v>
+        <v>0.00825</v>
       </c>
       <c r="H1" t="n">
-        <v>0.01511052631578948</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01762894736842106</v>
+        <v>0.01155</v>
       </c>
       <c r="J1" t="n">
-        <v>0.02014736842105263</v>
+        <v>0.0132</v>
       </c>
       <c r="K1" t="n">
-        <v>0.02266578947368422</v>
+        <v>0.01485</v>
       </c>
       <c r="L1" t="n">
-        <v>0.02518421052631579</v>
+        <v>0.0165</v>
       </c>
       <c r="M1" t="n">
-        <v>0.02770263157894737</v>
+        <v>0.01815</v>
       </c>
       <c r="N1" t="n">
-        <v>0.03022105263157895</v>
+        <v>0.0198</v>
       </c>
       <c r="O1" t="n">
-        <v>0.03273947368421053</v>
+        <v>0.02145</v>
       </c>
       <c r="P1" t="n">
-        <v>0.03525789473684211</v>
+        <v>0.0231</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.03777631578947369</v>
+        <v>0.02475</v>
       </c>
       <c r="R1" t="n">
-        <v>0.04029473684210527</v>
+        <v>0.0264</v>
       </c>
       <c r="S1" t="n">
-        <v>0.04281315789473685</v>
+        <v>0.02805</v>
       </c>
       <c r="T1" t="n">
-        <v>0.04533157894736843</v>
+        <v>0.0297</v>
       </c>
       <c r="U1" t="n">
+        <v>0.03135</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.03465</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.03630000000000001</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.03795</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.04455</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.04785</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.06435335611923917</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01928721174004193</v>
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.06435335611923917</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06435335611923917</v>
       </c>
     </row>
   </sheetData>
